--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +126,7 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +134,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -428,11 +430,11 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="22.00390625" customWidth="1" style="13" min="1" max="1"/>
-    <col width="19.140625" customWidth="1" style="13" min="2" max="2"/>
-    <col width="34.421875" customWidth="1" style="13" min="3" max="3"/>
-    <col width="18.7109375" customWidth="1" style="13" min="4" max="4"/>
-    <col width="14.57421875" customWidth="1" style="13" min="5" max="5"/>
+    <col width="22.00390625" customWidth="1" style="14" min="1" max="1"/>
+    <col width="19.140625" customWidth="1" style="14" min="2" max="2"/>
+    <col width="34.421875" customWidth="1" style="14" min="3" max="3"/>
+    <col width="18.7109375" customWidth="1" style="14" min="4" max="4"/>
+    <col width="14.57421875" customWidth="1" style="14" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,7 +448,7 @@
           <t xml:space="preserve"> Создан</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
@@ -468,7 +470,7 @@
     <row r="4"/>
     <row r="5"/>
     <row r="6"/>
-    <row r="7" ht="14.25" customHeight="1" s="13">
+    <row r="7" ht="14.25" customHeight="1" s="14">
       <c r="A7" s="3" t="n">
         <v>1</v>
       </c>
@@ -480,10 +482,10 @@
       <c r="C7" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>213.33</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>2222.33</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -519,7 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1" s="13">
+    <row r="9" ht="14.25" customHeight="1" s="14">
       <c r="A9" s="3" t="n">
         <v>1</v>
       </c>
@@ -531,19 +533,19 @@
       <c r="C9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>50.55</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>151.65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>&lt;- Для табличного вывода можно применять плайсхолдеры , но в настройках вывода таблицы, все равно нужно явно кузывать номер столбца для вывода</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1" s="13">
+          <t>&lt;- Для табличного вывода можно применять плайсхолдеры , но в настройках вывода таблицы, все равно нужно явно указывать номер столбца для вывода</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" s="14">
       <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
@@ -555,10 +557,10 @@
       <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>70.25</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>140.5</v>
       </c>
     </row>
@@ -579,7 +581,7 @@
           <t>Итого сумма:</t>
         </is>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="18" t="n">
         <v>292.15</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -592,14 +594,20 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="14.25" customHeight="1" s="13"/>
-    <row r="14">
-      <c r="A14" s="17" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16" ht="14.25" customHeight="1" s="13"/>
+    <row r="13" ht="14.25" customHeight="1" s="14"/>
+    <row r="14" ht="14.25" customHeight="1" s="14">
+      <c r="A14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Список лотов поставки: 1 ; 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" s="14"/>
     <row r="17">
-      <c r="E17" s="17" t="n"/>
+      <c r="E17" s="19" t="n"/>
     </row>
     <row r="18"/>
     <row r="19"/>
@@ -610,18 +618,12 @@
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
-    <row r="27" ht="14.25" customHeight="1" s="13"/>
-    <row r="28">
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Итого кол-во: 5.0</t>
-        </is>
-      </c>
-    </row>
+    <row r="27" ht="14.25" customHeight="1" s="14"/>
+    <row r="28"/>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
-    <row r="32" ht="14.25" customHeight="1" s="13"/>
+    <row r="32" ht="14.25" customHeight="1" s="14"/>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>02.06.2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
     </row>

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>09.06.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
     </row>

--- a/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
+++ b/pipelines/Demo_data/Output_data/group_export/Отчёт_Север_2025-Q1.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,11 +129,22 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -450,17 +461,17 @@
       </c>
       <c r="C1" s="15" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Группа: Север</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Период: 2025-Q1</t>
         </is>
@@ -525,19 +536,25 @@
       <c r="A9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Яблоко</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>50.55</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>151.65</v>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>50.55</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>151.64999999999998</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -549,29 +566,35 @@
       <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Груша</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>70.25</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>140.5</v>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>70.25</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Строк: 2.0</t>
         </is>
       </c>
       <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Итого кол-во: 5.0</t>
         </is>
@@ -581,7 +604,7 @@
           <t>Итого сумма:</t>
         </is>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="23" t="n">
         <v>292.15</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -596,10 +619,10 @@
     <row r="12"/>
     <row r="13" ht="14.25" customHeight="1" s="14"/>
     <row r="14" ht="14.25" customHeight="1" s="14">
-      <c r="A14" s="19" t="n"/>
+      <c r="A14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Список лотов поставки: 1 ; 2</t>
         </is>
@@ -607,7 +630,7 @@
     </row>
     <row r="16" ht="14.25" customHeight="1" s="14"/>
     <row r="17">
-      <c r="E17" s="19" t="n"/>
+      <c r="E17" s="24" t="n"/>
     </row>
     <row r="18"/>
     <row r="19"/>
@@ -625,7 +648,7 @@
     <row r="31"/>
     <row r="32" ht="14.25" customHeight="1" s="14"/>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Итого кол-во: 5.0</t>
         </is>
